--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_229_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_229_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8184</v>
+        <v>1.4687</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1143</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>1.3236</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8196</v>
+        <v>0.4698</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6201</v>
+        <v>0.472</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1994</v>
+        <v>-0.0022</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1963</v>
+        <v>1.365</v>
       </c>
       <c r="E3" t="n">
-        <v>3.371</v>
+        <v>3.6069</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1747</v>
+        <v>-2.2419</v>
       </c>
       <c r="G3" t="n">
         <v>3.4317</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3618</v>
+        <v>-1.1931</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1949</v>
+        <v>-0.959</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1669</v>
+        <v>-0.2341</v>
       </c>
       <c r="V3" t="n">
         <v>1.214</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6532</v>
+        <v>1.2908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5145999999999999</v>
+        <v>1.0178</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1386</v>
+        <v>0.273</v>
       </c>
       <c r="G4" t="n">
         <v>1.5502</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.129</v>
+        <v>-0.4914</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.963</v>
+        <v>-0.4597</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1661</v>
+        <v>-0.0316</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.595</v>
+        <v>1.0229</v>
       </c>
       <c r="E5" t="n">
-        <v>1.509</v>
+        <v>1.7017</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9141</v>
+        <v>-0.6788</v>
       </c>
       <c r="G5" t="n">
         <v>1.8679</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3605</v>
+        <v>-0.9326</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8883</v>
+        <v>-0.6956</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4722</v>
+        <v>-0.237</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1152</v>
+        <v>-0.0974</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5952</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.48</v>
+        <v>-0.1776</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2086</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3238</v>
+        <v>0.1111</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6765</v>
+        <v>0.1614</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3528</v>
+        <v>-0.0503</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9149</v>
+        <v>-1.1508</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2328</v>
+        <v>-0.0031</v>
       </c>
       <c r="F7" t="n">
         <v>-1.1477</v>
@@ -1000,10 +1000,10 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2557</v>
+        <v>0.0198</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1221</v>
+        <v>-0.1138</v>
       </c>
       <c r="U7" t="n">
         <v>0.1336</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8912</v>
+        <v>-1.9749</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7047</v>
+        <v>-2.5868</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8135</v>
+        <v>0.6119</v>
       </c>
       <c r="G8" t="n">
         <v>-2.9886</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2996</v>
+        <v>-0.3833</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2978</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>1.8608</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6654</v>
+        <v>-3.5555</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4205</v>
+        <v>-2.161</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0859</v>
+        <v>-1.3945</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3505</v>
+        <v>-2.1356</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1259</v>
+        <v>-2.0252</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2246</v>
+        <v>-0.1104</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-1.0913</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0504</v>
+        <v>-0.9306</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.1607</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6514</v>
+        <v>-1.0443</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1763</v>
+        <v>-1.0945</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4751</v>
+        <v>0.0502</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4532</v>
+        <v>0.0492</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2072</v>
+        <v>0.2008</v>
       </c>
       <c r="U9" t="n">
-        <v>0.246</v>
+        <v>-0.1516</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>-2.3969</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>-0.1107</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ATAMNA</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2062</v>
+        <v>-3.5583</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9249</v>
+        <v>-0.4052</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7187</v>
+        <v>-3.1531</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.712</v>
+        <v>-2.3505</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4538</v>
+        <v>-1.1259</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2582</v>
+        <v>-1.2246</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.8477</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.275</v>
+        <v>0.0504</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5727</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1357</v>
+        <v>-1.6514</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1788</v>
+        <v>-1.1763</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3145</v>
+        <v>-0.4751</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4336</v>
+        <v>0.5603</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.3815</v>
       </c>
       <c r="U10" t="n">
-        <v>0.351</v>
+        <v>0.1788</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>A. ATAMNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3454</v>
+        <v>-3.6501</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0181</v>
+        <v>-4.3351</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3273</v>
+        <v>0.6851</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1356</v>
+        <v>-3.712</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0252</v>
+        <v>-2.4538</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1104</v>
+        <v>-1.2582</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0913</v>
+        <v>-3.8477</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9306</v>
+        <v>-2.275</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1607</v>
+        <v>-1.5727</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0443</v>
+        <v>0.1357</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0945</v>
+        <v>-0.1788</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0502</v>
+        <v>0.3145</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7407</v>
+        <v>0.9897</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6563</v>
+        <v>0.6723</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0843</v>
+        <v>0.3174</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3969</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1107</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8585</v>
+        <v>-4.4807</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4927</v>
+        <v>-0.1821</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3658</v>
+        <v>-4.2986</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4782</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1817</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8136</v>
+        <v>-0.503</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3681</v>
+        <v>-0.3009</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8223</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9418</v>
+        <v>-7.3782</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5179</v>
+        <v>-4.8534</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.424</v>
+        <v>-2.5248</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6398</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0004</v>
+        <v>0.5632</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4402</v>
+        <v>0.2243</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4397</v>
+        <v>0.3389</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8223</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.4453</v>
+        <v>-20.6985</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.9009</v>
+        <v>-7.153899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.5446</v>
+        <v>-13.5445</v>
       </c>
       <c r="G14" t="n">
         <v>-9.4383</v>
@@ -1516,10 +1516,10 @@
         <v>-11.2784</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8403</v>
+        <v>1.840300000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5776</v>
+        <v>5.577600000000002</v>
       </c>
       <c r="K14" t="n">
         <v>1.864199999999999</v>
@@ -1546,13 +1546,13 @@
         <v>13.9174</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7878</v>
+        <v>-1.041199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8453</v>
+        <v>-1.0983</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05710000000000004</v>
+        <v>0.05719999999999997</v>
       </c>
       <c r="V14" t="n">
         <v>-7.899699999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.155200000000001</v>
+        <v>8.241400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0756</v>
+        <v>4.3954</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0796</v>
+        <v>3.846</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1687</v>
+        <v>5.5017</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9674</v>
+        <v>3.8689</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2012</v>
+        <v>1.6327</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2108</v>
+        <v>4.7011</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2673</v>
+        <v>3.0116</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9435</v>
+        <v>1.6895</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9579</v>
+        <v>0.8006</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2578</v>
+        <v>-0.0568</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2854</v>
+        <v>0.6829</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8259</v>
+        <v>-0.0431</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4595</v>
+        <v>0.726</v>
       </c>
       <c r="V15" t="n">
-        <v>3.4691</v>
+        <v>3.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3584</v>
+        <v>3.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.049200000000001</v>
+        <v>7.308</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9236</v>
+        <v>3.2499</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1257</v>
+        <v>4.0581</v>
       </c>
       <c r="G16" t="n">
-        <v>5.5017</v>
+        <v>3.1687</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8689</v>
+        <v>1.9674</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6327</v>
+        <v>1.2012</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7011</v>
+        <v>2.2108</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0116</v>
+        <v>1.2673</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6895</v>
+        <v>0.9435</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8006</v>
+        <v>0.9579</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0568</v>
+        <v>0.2578</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3195</v>
+        <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4907</v>
+        <v>0.4382</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5149</v>
+        <v>0.0002</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0056</v>
+        <v>0.438</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2166</v>
+        <v>3.4691</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2166</v>
+        <v>3.3584</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7882</v>
+        <v>4.1636</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0247</v>
+        <v>0.9067</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7635</v>
+        <v>3.2569</v>
       </c>
       <c r="G17" t="n">
         <v>0.3139</v>
@@ -1780,13 +1780,13 @@
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3145</v>
+        <v>0.6899</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3462</v>
+        <v>0.2282</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0316</v>
+        <v>0.4617</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1949</v>
+        <v>2.3421</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3032</v>
+        <v>0.1595</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1083</v>
+        <v>2.1826</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8486</v>
+        <v>1.5168</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9996</v>
+        <v>2.2328</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.151</v>
+        <v>-0.716</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5912</v>
+        <v>2.0566</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2671</v>
+        <v>1.983</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2574</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.2499</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4751</v>
+        <v>-0.7896</v>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.3195</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.5515</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.1738</v>
+        <v>0.1474</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3383</v>
+        <v>-0.2555</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8356</v>
+        <v>0.4028</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.147</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.7527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9254</v>
+        <v>2.167</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0051</v>
+        <v>2.1852</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0797</v>
+        <v>-0.0183</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9607</v>
+        <v>2.8486</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0599</v>
+        <v>3.9996</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0206</v>
+        <v>-1.151</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6614</v>
+        <v>2.5912</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3732</v>
+        <v>3.2671</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2882</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7007</v>
+        <v>0.2574</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4331</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2676</v>
+        <v>-0.4751</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0369</v>
+        <v>1.1459</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2715</v>
+        <v>0.2203</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2346</v>
+        <v>0.9256</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-4.147</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7308</v>
+        <v>1.914</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0416</v>
+        <v>2.7691</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6893</v>
+        <v>-0.8552</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5168</v>
+        <v>0.9607</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2328</v>
+        <v>-0.0599</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.716</v>
+        <v>1.0206</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0566</v>
+        <v>1.6614</v>
       </c>
       <c r="K20" t="n">
-        <v>1.983</v>
+        <v>0.3732</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>1.2882</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.7007</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2499</v>
+        <v>-0.4331</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7896</v>
+        <v>-0.2676</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4639</v>
+        <v>0.0255</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>0.0356</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0905</v>
+        <v>-0.0101</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7054</v>
+        <v>1.8805</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3707</v>
+        <v>1.7245</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3348</v>
+        <v>0.156</v>
       </c>
       <c r="G21" t="n">
         <v>1.0491</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1924</v>
+        <v>0.3675</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4402</v>
+        <v>-0.0863</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.4538</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9283</v>
+        <v>0.6645</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7337</v>
+        <v>0.3799</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1946</v>
+        <v>0.2846</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6969</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1792</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3084</v>
+        <v>-0.2183</v>
       </c>
       <c r="V22" t="n">
         <v>1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.031</v>
+        <v>0.2498</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1617</v>
+        <v>1.2796</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1307</v>
+        <v>-1.0299</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8844</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3888</v>
+        <v>-0.17</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2339</v>
+        <v>-0.7281</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6726</v>
+        <v>-0.0516</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4387</v>
+        <v>-0.6765</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1863</v>
+        <v>-1.9731</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8282</v>
+        <v>-1.1199</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3581</v>
+        <v>-0.8532</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3833</v>
+        <v>-0.0678</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4236</v>
+        <v>-0.215</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0403</v>
+        <v>0.1472</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5696</v>
+        <v>-1.9053</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2518</v>
+        <v>-0.9049</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3178</v>
+        <v>-1.0004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2539</v>
+        <v>0.3145</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2636</v>
+        <v>0.1063</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0097</v>
+        <v>0.2082</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3943</v>
+        <v>0.9304</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3943</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4688</v>
+        <v>-1.1439</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5234</v>
+        <v>-1.6726</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9454</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9731</v>
+        <v>-1.1863</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1199</v>
+        <v>-0.8282</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8532</v>
+        <v>-0.3581</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0678</v>
+        <v>0.3833</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.215</v>
+        <v>0.4236</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1472</v>
+        <v>-0.0403</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9053</v>
+        <v>-1.5696</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9049</v>
+        <v>-1.2518</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0004</v>
+        <v>-0.3178</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R25" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4261</v>
+        <v>0.344</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3655</v>
+        <v>0.2636</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0606</v>
+        <v>0.0804</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9304</v>
+        <v>0.3943</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7886</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3605</v>
+        <v>-4.0409</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9713</v>
+        <v>-2.8533</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3892</v>
+        <v>-1.1876</v>
       </c>
       <c r="G26" t="n">
         <v>-1.1808</v>
@@ -2482,13 +2482,13 @@
         <v>0.232</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8602</v>
+        <v>-0.5406</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2627</v>
+        <v>-0.0611</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>21.4452</v>
+        <v>23.018</v>
       </c>
       <c r="E27" t="n">
-        <v>12.4726</v>
+        <v>12.4723</v>
       </c>
       <c r="F27" t="n">
-        <v>8.972900000000001</v>
+        <v>10.5454</v>
       </c>
       <c r="G27" t="n">
-        <v>9.437999999999999</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>11.2783</v>
@@ -2560,13 +2560,13 @@
         <v>16.2369</v>
       </c>
       <c r="S27" t="n">
-        <v>1.787800000000001</v>
+        <v>3.3606</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.05710000000000004</v>
+        <v>-0.05719999999999997</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8451</v>
+        <v>3.4178</v>
       </c>
       <c r="V27" t="n">
         <v>7.899700000000001</v>
